--- a/output/Daily_Route_Summary_normal.xlsx
+++ b/output/Daily_Route_Summary_normal.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>driver</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>driver_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>stop_count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>service_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>drive_min</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dist_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>total_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>overtime_min</t>
         </is>
@@ -478,19 +490,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="F2" t="n">
-        <v>111.88</v>
+        <v>124.31</v>
       </c>
       <c r="G2" t="n">
-        <v>65.26000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>319.88</v>
+        <v>316.31</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -511,19 +523,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>112.94</v>
+        <v>117.9</v>
       </c>
       <c r="G3" t="n">
-        <v>65.88</v>
+        <v>68.78</v>
       </c>
       <c r="H3" t="n">
-        <v>320.94</v>
+        <v>317.9</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -550,13 +562,13 @@
         <v>188</v>
       </c>
       <c r="F4" t="n">
-        <v>129.37</v>
+        <v>127.37</v>
       </c>
       <c r="G4" t="n">
-        <v>75.47</v>
+        <v>74.3</v>
       </c>
       <c r="H4" t="n">
-        <v>317.37</v>
+        <v>315.37</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -577,19 +589,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F5" t="n">
-        <v>100.89</v>
+        <v>102.07</v>
       </c>
       <c r="G5" t="n">
-        <v>58.85</v>
+        <v>59.54</v>
       </c>
       <c r="H5" t="n">
-        <v>316.89</v>
+        <v>326.07</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -610,19 +622,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="F6" t="n">
-        <v>117.23</v>
+        <v>141.05</v>
       </c>
       <c r="G6" t="n">
-        <v>68.38</v>
+        <v>82.28</v>
       </c>
       <c r="H6" t="n">
-        <v>327.23</v>
+        <v>319.05</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -643,19 +655,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F7" t="n">
-        <v>119.51</v>
+        <v>115.05</v>
       </c>
       <c r="G7" t="n">
-        <v>69.70999999999999</v>
+        <v>67.11</v>
       </c>
       <c r="H7" t="n">
-        <v>319.51</v>
+        <v>323.05</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -682,13 +694,13 @@
         <v>192</v>
       </c>
       <c r="F8" t="n">
-        <v>128.41</v>
+        <v>126.19</v>
       </c>
       <c r="G8" t="n">
-        <v>74.91</v>
+        <v>73.61</v>
       </c>
       <c r="H8" t="n">
-        <v>320.41</v>
+        <v>318.19</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -709,19 +721,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="F9" t="n">
-        <v>132.38</v>
+        <v>117.63</v>
       </c>
       <c r="G9" t="n">
-        <v>77.22</v>
+        <v>68.62</v>
       </c>
       <c r="H9" t="n">
-        <v>316.38</v>
+        <v>325.63</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -748,13 +760,13 @@
         <v>208</v>
       </c>
       <c r="F10" t="n">
-        <v>113.92</v>
+        <v>106.99</v>
       </c>
       <c r="G10" t="n">
-        <v>66.45</v>
+        <v>62.41</v>
       </c>
       <c r="H10" t="n">
-        <v>321.92</v>
+        <v>314.99</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -775,19 +787,19 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F11" t="n">
-        <v>131.14</v>
+        <v>129.31</v>
       </c>
       <c r="G11" t="n">
-        <v>76.5</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>315.14</v>
+        <v>321.31</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -808,19 +820,19 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F12" t="n">
-        <v>133.25</v>
+        <v>132.56</v>
       </c>
       <c r="G12" t="n">
-        <v>77.73</v>
+        <v>77.33</v>
       </c>
       <c r="H12" t="n">
-        <v>325.25</v>
+        <v>316.56</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -847,13 +859,13 @@
         <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>103.87</v>
+        <v>108.78</v>
       </c>
       <c r="G13" t="n">
-        <v>60.59</v>
+        <v>63.46</v>
       </c>
       <c r="H13" t="n">
-        <v>319.87</v>
+        <v>324.78</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -874,19 +886,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F14" t="n">
-        <v>138.05</v>
+        <v>138.9</v>
       </c>
       <c r="G14" t="n">
-        <v>80.53</v>
+        <v>81.02</v>
       </c>
       <c r="H14" t="n">
-        <v>322.05</v>
+        <v>314.9</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -913,13 +925,13 @@
         <v>169</v>
       </c>
       <c r="F15" t="n">
-        <v>150.35</v>
+        <v>153.9</v>
       </c>
       <c r="G15" t="n">
-        <v>87.7</v>
+        <v>89.77</v>
       </c>
       <c r="H15" t="n">
-        <v>319.35</v>
+        <v>322.9</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -940,19 +952,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="F16" t="n">
-        <v>124.84</v>
+        <v>141.38</v>
       </c>
       <c r="G16" t="n">
-        <v>72.81999999999999</v>
+        <v>82.47</v>
       </c>
       <c r="H16" t="n">
-        <v>324.84</v>
+        <v>325.38</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -973,19 +985,19 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F17" t="n">
-        <v>118.61</v>
+        <v>126.85</v>
       </c>
       <c r="G17" t="n">
-        <v>69.19</v>
+        <v>74</v>
       </c>
       <c r="H17" t="n">
-        <v>318.61</v>
+        <v>318.85</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1012,13 +1024,13 @@
         <v>216</v>
       </c>
       <c r="F18" t="n">
-        <v>106.25</v>
+        <v>110.68</v>
       </c>
       <c r="G18" t="n">
-        <v>61.98</v>
+        <v>64.56</v>
       </c>
       <c r="H18" t="n">
-        <v>322.25</v>
+        <v>326.68</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1045,13 +1057,13 @@
         <v>216</v>
       </c>
       <c r="F19" t="n">
-        <v>106.03</v>
+        <v>105.29</v>
       </c>
       <c r="G19" t="n">
-        <v>61.85</v>
+        <v>61.42</v>
       </c>
       <c r="H19" t="n">
-        <v>322.03</v>
+        <v>321.29</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1078,13 +1090,13 @@
         <v>184</v>
       </c>
       <c r="F20" t="n">
-        <v>133.68</v>
+        <v>134.42</v>
       </c>
       <c r="G20" t="n">
-        <v>77.98</v>
+        <v>78.41</v>
       </c>
       <c r="H20" t="n">
-        <v>317.68</v>
+        <v>318.42</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1111,13 +1123,13 @@
         <v>192</v>
       </c>
       <c r="F21" t="n">
-        <v>133.66</v>
+        <v>132.17</v>
       </c>
       <c r="G21" t="n">
-        <v>77.97</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>325.66</v>
+        <v>324.17</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1144,13 +1156,13 @@
         <v>198</v>
       </c>
       <c r="F22" t="n">
-        <v>119.01</v>
+        <v>120.23</v>
       </c>
       <c r="G22" t="n">
-        <v>69.42</v>
+        <v>70.13</v>
       </c>
       <c r="H22" t="n">
-        <v>317.01</v>
+        <v>318.23</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1177,13 +1189,13 @@
         <v>168</v>
       </c>
       <c r="F23" t="n">
-        <v>148.12</v>
+        <v>150.14</v>
       </c>
       <c r="G23" t="n">
-        <v>86.40000000000001</v>
+        <v>87.58</v>
       </c>
       <c r="H23" t="n">
-        <v>316.12</v>
+        <v>318.14</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1204,19 +1216,19 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F24" t="n">
-        <v>93.95999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="G24" t="n">
-        <v>54.81</v>
+        <v>53.27</v>
       </c>
       <c r="H24" t="n">
-        <v>325.96</v>
+        <v>315.33</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1237,19 +1249,19 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F25" t="n">
-        <v>115.37</v>
+        <v>100.6</v>
       </c>
       <c r="G25" t="n">
-        <v>67.3</v>
+        <v>58.69</v>
       </c>
       <c r="H25" t="n">
-        <v>315.37</v>
+        <v>324.6</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1276,13 +1288,13 @@
         <v>196</v>
       </c>
       <c r="F26" t="n">
-        <v>120.72</v>
+        <v>121.88</v>
       </c>
       <c r="G26" t="n">
-        <v>70.42</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>316.72</v>
+        <v>317.88</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1303,19 +1315,19 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F27" t="n">
-        <v>121.13</v>
+        <v>117.87</v>
       </c>
       <c r="G27" t="n">
-        <v>70.66</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>317.13</v>
+        <v>321.87</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1336,19 +1348,19 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F28" t="n">
-        <v>96.94</v>
+        <v>96.86</v>
       </c>
       <c r="G28" t="n">
-        <v>56.55</v>
+        <v>56.5</v>
       </c>
       <c r="H28" t="n">
-        <v>322.94</v>
+        <v>314.86</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1369,19 +1381,19 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F29" t="n">
-        <v>131.62</v>
+        <v>135.15</v>
       </c>
       <c r="G29" t="n">
-        <v>76.78</v>
+        <v>78.84</v>
       </c>
       <c r="H29" t="n">
-        <v>323.62</v>
+        <v>319.15</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1408,13 +1420,13 @@
         <v>216</v>
       </c>
       <c r="F30" t="n">
-        <v>107.78</v>
+        <v>103.07</v>
       </c>
       <c r="G30" t="n">
-        <v>62.87</v>
+        <v>60.13</v>
       </c>
       <c r="H30" t="n">
-        <v>323.78</v>
+        <v>319.07</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1441,13 +1453,13 @@
         <v>208</v>
       </c>
       <c r="F31" t="n">
-        <v>108.09</v>
+        <v>113.14</v>
       </c>
       <c r="G31" t="n">
-        <v>63.05</v>
+        <v>66</v>
       </c>
       <c r="H31" t="n">
-        <v>316.09</v>
+        <v>321.14</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1474,13 +1486,13 @@
         <v>208</v>
       </c>
       <c r="F32" t="n">
-        <v>114.53</v>
+        <v>107.87</v>
       </c>
       <c r="G32" t="n">
-        <v>66.81</v>
+        <v>62.93</v>
       </c>
       <c r="H32" t="n">
-        <v>322.53</v>
+        <v>315.87</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1501,19 +1513,19 @@
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F33" t="n">
-        <v>146.76</v>
+        <v>142.86</v>
       </c>
       <c r="G33" t="n">
-        <v>85.61</v>
+        <v>83.33</v>
       </c>
       <c r="H33" t="n">
-        <v>314.76</v>
+        <v>318.86</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1534,19 +1546,19 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F34" t="n">
-        <v>147.01</v>
+        <v>147.66</v>
       </c>
       <c r="G34" t="n">
-        <v>85.76000000000001</v>
+        <v>86.14</v>
       </c>
       <c r="H34" t="n">
-        <v>315.01</v>
+        <v>323.66</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1573,13 +1585,13 @@
         <v>200</v>
       </c>
       <c r="F35" t="n">
-        <v>124.57</v>
+        <v>125</v>
       </c>
       <c r="G35" t="n">
-        <v>72.67</v>
+        <v>72.92</v>
       </c>
       <c r="H35" t="n">
-        <v>324.57</v>
+        <v>325</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -1600,19 +1612,19 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F36" t="n">
-        <v>148.42</v>
+        <v>142.57</v>
       </c>
       <c r="G36" t="n">
-        <v>86.58</v>
+        <v>83.17</v>
       </c>
       <c r="H36" t="n">
-        <v>324.42</v>
+        <v>326.57</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -1639,13 +1651,13 @@
         <v>192</v>
       </c>
       <c r="F37" t="n">
-        <v>124.19</v>
+        <v>129.39</v>
       </c>
       <c r="G37" t="n">
-        <v>72.44</v>
+        <v>75.48</v>
       </c>
       <c r="H37" t="n">
-        <v>316.19</v>
+        <v>321.39</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1666,19 +1678,19 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F38" t="n">
-        <v>140.41</v>
+        <v>133.37</v>
       </c>
       <c r="G38" t="n">
-        <v>81.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H38" t="n">
-        <v>324.41</v>
+        <v>325.37</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1705,13 +1717,13 @@
         <v>193</v>
       </c>
       <c r="F39" t="n">
-        <v>127.25</v>
+        <v>122.7</v>
       </c>
       <c r="G39" t="n">
-        <v>74.23</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>320.25</v>
+        <v>315.7</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1732,19 +1744,19 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F40" t="n">
-        <v>120.73</v>
+        <v>127.43</v>
       </c>
       <c r="G40" t="n">
-        <v>70.42</v>
+        <v>74.33</v>
       </c>
       <c r="H40" t="n">
-        <v>325.73</v>
+        <v>324.43</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1771,13 +1783,13 @@
         <v>200</v>
       </c>
       <c r="F41" t="n">
-        <v>119.74</v>
+        <v>121.57</v>
       </c>
       <c r="G41" t="n">
-        <v>69.84999999999999</v>
+        <v>70.92</v>
       </c>
       <c r="H41" t="n">
-        <v>319.74</v>
+        <v>321.57</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1798,19 +1810,19 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F42" t="n">
-        <v>105.33</v>
+        <v>111.99</v>
       </c>
       <c r="G42" t="n">
-        <v>61.44</v>
+        <v>65.33</v>
       </c>
       <c r="H42" t="n">
-        <v>321.33</v>
+        <v>319.99</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -1837,13 +1849,13 @@
         <v>192</v>
       </c>
       <c r="F43" t="n">
-        <v>123.49</v>
+        <v>126.61</v>
       </c>
       <c r="G43" t="n">
-        <v>72.03</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>315.49</v>
+        <v>318.61</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -1870,13 +1882,13 @@
         <v>168</v>
       </c>
       <c r="F44" t="n">
-        <v>153.22</v>
+        <v>153.94</v>
       </c>
       <c r="G44" t="n">
-        <v>89.38</v>
+        <v>89.8</v>
       </c>
       <c r="H44" t="n">
-        <v>321.22</v>
+        <v>321.94</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -1897,19 +1909,19 @@
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F45" t="n">
-        <v>105.49</v>
+        <v>109.61</v>
       </c>
       <c r="G45" t="n">
-        <v>61.54</v>
+        <v>63.94</v>
       </c>
       <c r="H45" t="n">
-        <v>321.49</v>
+        <v>317.61</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -1936,13 +1948,13 @@
         <v>208</v>
       </c>
       <c r="F46" t="n">
-        <v>113.6</v>
+        <v>110.95</v>
       </c>
       <c r="G46" t="n">
-        <v>66.27</v>
+        <v>64.72</v>
       </c>
       <c r="H46" t="n">
-        <v>321.6</v>
+        <v>318.95</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -1963,19 +1975,19 @@
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F47" t="n">
-        <v>138.06</v>
+        <v>138.71</v>
       </c>
       <c r="G47" t="n">
-        <v>80.54000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="H47" t="n">
-        <v>322.06</v>
+        <v>314.71</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2002,13 +2014,13 @@
         <v>200</v>
       </c>
       <c r="F48" t="n">
-        <v>120.83</v>
+        <v>120.16</v>
       </c>
       <c r="G48" t="n">
-        <v>70.48999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="H48" t="n">
-        <v>320.83</v>
+        <v>320.16</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2035,13 +2047,13 @@
         <v>192</v>
       </c>
       <c r="F49" t="n">
-        <v>125.66</v>
+        <v>125.9</v>
       </c>
       <c r="G49" t="n">
-        <v>73.3</v>
+        <v>73.44</v>
       </c>
       <c r="H49" t="n">
-        <v>317.66</v>
+        <v>317.9</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2062,19 +2074,19 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F50" t="n">
-        <v>121.3</v>
+        <v>114.24</v>
       </c>
       <c r="G50" t="n">
-        <v>70.76000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="H50" t="n">
-        <v>321.3</v>
+        <v>322.24</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2095,19 +2107,19 @@
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F51" t="n">
-        <v>118.27</v>
+        <v>121.84</v>
       </c>
       <c r="G51" t="n">
-        <v>68.98999999999999</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>324.27</v>
+        <v>319.84</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2134,13 +2146,13 @@
         <v>208</v>
       </c>
       <c r="F52" t="n">
-        <v>109.11</v>
+        <v>111.51</v>
       </c>
       <c r="G52" t="n">
-        <v>63.64</v>
+        <v>65.05</v>
       </c>
       <c r="H52" t="n">
-        <v>317.11</v>
+        <v>319.51</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2167,13 +2179,13 @@
         <v>216</v>
       </c>
       <c r="F53" t="n">
-        <v>107.59</v>
+        <v>110.19</v>
       </c>
       <c r="G53" t="n">
-        <v>62.76</v>
+        <v>64.28</v>
       </c>
       <c r="H53" t="n">
-        <v>323.59</v>
+        <v>326.19</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2194,19 +2206,19 @@
         <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="F54" t="n">
-        <v>135.72</v>
+        <v>107.2</v>
       </c>
       <c r="G54" t="n">
-        <v>79.17</v>
+        <v>62.53</v>
       </c>
       <c r="H54" t="n">
-        <v>323.72</v>
+        <v>319.2</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2233,13 +2245,13 @@
         <v>208</v>
       </c>
       <c r="F55" t="n">
-        <v>108.57</v>
+        <v>107.53</v>
       </c>
       <c r="G55" t="n">
-        <v>63.33</v>
+        <v>62.73</v>
       </c>
       <c r="H55" t="n">
-        <v>316.57</v>
+        <v>315.53</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -2266,13 +2278,13 @@
         <v>176</v>
       </c>
       <c r="F56" t="n">
-        <v>145.37</v>
+        <v>143.88</v>
       </c>
       <c r="G56" t="n">
-        <v>84.8</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>321.37</v>
+        <v>319.88</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2293,19 +2305,19 @@
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F57" t="n">
-        <v>142.39</v>
+        <v>136.38</v>
       </c>
       <c r="G57" t="n">
-        <v>83.06</v>
+        <v>79.56</v>
       </c>
       <c r="H57" t="n">
-        <v>318.39</v>
+        <v>320.38</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2326,19 +2338,19 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E58" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F58" t="n">
-        <v>121.2</v>
+        <v>127.83</v>
       </c>
       <c r="G58" t="n">
-        <v>70.7</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>326.2</v>
+        <v>324.83</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2359,19 +2371,19 @@
         <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F59" t="n">
-        <v>141.01</v>
+        <v>127.15</v>
       </c>
       <c r="G59" t="n">
-        <v>82.26000000000001</v>
+        <v>74.17</v>
       </c>
       <c r="H59" t="n">
-        <v>325.01</v>
+        <v>319.15</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2392,19 +2404,19 @@
         <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F60" t="n">
-        <v>128.49</v>
+        <v>140.29</v>
       </c>
       <c r="G60" t="n">
-        <v>74.95</v>
+        <v>81.84</v>
       </c>
       <c r="H60" t="n">
-        <v>320.49</v>
+        <v>316.29</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -2425,19 +2437,19 @@
         <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F61" t="n">
-        <v>124.16</v>
+        <v>118.14</v>
       </c>
       <c r="G61" t="n">
-        <v>72.43000000000001</v>
+        <v>68.91</v>
       </c>
       <c r="H61" t="n">
-        <v>316.16</v>
+        <v>318.14</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -2464,13 +2476,13 @@
         <v>200</v>
       </c>
       <c r="F62" t="n">
-        <v>116.02</v>
+        <v>115.38</v>
       </c>
       <c r="G62" t="n">
-        <v>67.68000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="H62" t="n">
-        <v>316.02</v>
+        <v>315.38</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2491,19 +2503,19 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E63" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F63" t="n">
-        <v>107.63</v>
+        <v>112.41</v>
       </c>
       <c r="G63" t="n">
-        <v>62.78</v>
+        <v>65.58</v>
       </c>
       <c r="H63" t="n">
-        <v>323.63</v>
+        <v>320.41</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -2524,19 +2536,19 @@
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F64" t="n">
-        <v>134.38</v>
+        <v>127.07</v>
       </c>
       <c r="G64" t="n">
-        <v>78.39</v>
+        <v>74.12</v>
       </c>
       <c r="H64" t="n">
-        <v>318.38</v>
+        <v>319.07</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2557,19 +2569,19 @@
         <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F65" t="n">
-        <v>132.52</v>
+        <v>127.4</v>
       </c>
       <c r="G65" t="n">
-        <v>77.31</v>
+        <v>74.31</v>
       </c>
       <c r="H65" t="n">
-        <v>316.52</v>
+        <v>319.4</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -2596,13 +2608,13 @@
         <v>168</v>
       </c>
       <c r="F66" t="n">
-        <v>150.25</v>
+        <v>151.3</v>
       </c>
       <c r="G66" t="n">
-        <v>87.65000000000001</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>318.25</v>
+        <v>319.3</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -2623,19 +2635,19 @@
         <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E67" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F67" t="n">
-        <v>126.03</v>
+        <v>119.25</v>
       </c>
       <c r="G67" t="n">
-        <v>73.51000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="H67" t="n">
-        <v>318.03</v>
+        <v>319.25</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -2662,13 +2674,13 @@
         <v>208</v>
       </c>
       <c r="F68" t="n">
-        <v>115.26</v>
+        <v>110.46</v>
       </c>
       <c r="G68" t="n">
-        <v>67.23</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>323.26</v>
+        <v>318.46</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -2695,13 +2707,13 @@
         <v>200</v>
       </c>
       <c r="F69" t="n">
-        <v>119.11</v>
+        <v>115.29</v>
       </c>
       <c r="G69" t="n">
-        <v>69.48</v>
+        <v>67.25</v>
       </c>
       <c r="H69" t="n">
-        <v>319.11</v>
+        <v>315.29</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -2728,13 +2740,13 @@
         <v>168</v>
       </c>
       <c r="F70" t="n">
-        <v>155.39</v>
+        <v>151.88</v>
       </c>
       <c r="G70" t="n">
-        <v>90.64</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>323.39</v>
+        <v>319.88</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -2761,13 +2773,13 @@
         <v>204</v>
       </c>
       <c r="F71" t="n">
-        <v>119.19</v>
+        <v>119.95</v>
       </c>
       <c r="G71" t="n">
-        <v>69.53</v>
+        <v>69.97</v>
       </c>
       <c r="H71" t="n">
-        <v>323.19</v>
+        <v>323.95</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -2788,19 +2800,19 @@
         <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E72" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F72" t="n">
-        <v>131.11</v>
+        <v>129.52</v>
       </c>
       <c r="G72" t="n">
-        <v>76.48</v>
+        <v>75.55</v>
       </c>
       <c r="H72" t="n">
-        <v>317.11</v>
+        <v>323.52</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -2827,13 +2839,13 @@
         <v>186</v>
       </c>
       <c r="F73" t="n">
-        <v>133.75</v>
+        <v>132.62</v>
       </c>
       <c r="G73" t="n">
-        <v>78.02</v>
+        <v>77.36</v>
       </c>
       <c r="H73" t="n">
-        <v>319.75</v>
+        <v>318.62</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -2854,22 +2866,22 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E74" t="n">
-        <v>248</v>
+        <v>438</v>
       </c>
       <c r="F74" t="n">
-        <v>57.62</v>
+        <v>145.29</v>
       </c>
       <c r="G74" t="n">
-        <v>33.61</v>
+        <v>84.75</v>
       </c>
       <c r="H74" t="n">
-        <v>305.62</v>
+        <v>583.29</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="75">
@@ -2887,22 +2899,22 @@
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E75" t="n">
-        <v>198</v>
+        <v>427.5</v>
       </c>
       <c r="F75" t="n">
-        <v>110.69</v>
+        <v>158.53</v>
       </c>
       <c r="G75" t="n">
-        <v>64.56999999999999</v>
+        <v>92.48</v>
       </c>
       <c r="H75" t="n">
-        <v>308.69</v>
+        <v>586.03</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="76">
@@ -2920,22 +2932,22 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E76" t="n">
-        <v>184</v>
+        <v>422</v>
       </c>
       <c r="F76" t="n">
-        <v>121.61</v>
+        <v>160.87</v>
       </c>
       <c r="G76" t="n">
-        <v>70.94</v>
+        <v>93.84</v>
       </c>
       <c r="H76" t="n">
-        <v>305.61</v>
+        <v>582.87</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="77">
@@ -2953,22 +2965,22 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E77" t="n">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="F77" t="n">
-        <v>194.88</v>
+        <v>219.6</v>
       </c>
       <c r="G77" t="n">
-        <v>113.68</v>
+        <v>128.1</v>
       </c>
       <c r="H77" t="n">
-        <v>306.88</v>
+        <v>587.6</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="78">
@@ -2986,22 +2998,22 @@
         <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>144</v>
+        <v>393</v>
       </c>
       <c r="F78" t="n">
-        <v>163.65</v>
+        <v>192.82</v>
       </c>
       <c r="G78" t="n">
-        <v>95.45999999999999</v>
+        <v>112.48</v>
       </c>
       <c r="H78" t="n">
-        <v>307.65</v>
+        <v>585.8200000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="79">
@@ -3019,22 +3031,22 @@
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E79" t="n">
-        <v>192</v>
+        <v>369</v>
       </c>
       <c r="F79" t="n">
-        <v>114.64</v>
+        <v>212.24</v>
       </c>
       <c r="G79" t="n">
-        <v>66.88</v>
+        <v>123.81</v>
       </c>
       <c r="H79" t="n">
-        <v>306.64</v>
+        <v>581.24</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="80">
@@ -3052,22 +3064,22 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E80" t="n">
-        <v>120</v>
+        <v>368</v>
       </c>
       <c r="F80" t="n">
-        <v>181.02</v>
+        <v>212.64</v>
       </c>
       <c r="G80" t="n">
-        <v>105.59</v>
+        <v>124.04</v>
       </c>
       <c r="H80" t="n">
-        <v>301.02</v>
+        <v>580.64</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="81">
@@ -3085,22 +3097,22 @@
         <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E81" t="n">
-        <v>176</v>
+        <v>403</v>
       </c>
       <c r="F81" t="n">
-        <v>132.56</v>
+        <v>182.55</v>
       </c>
       <c r="G81" t="n">
-        <v>77.33</v>
+        <v>106.49</v>
       </c>
       <c r="H81" t="n">
-        <v>308.56</v>
+        <v>585.55</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="82">
@@ -3118,22 +3130,22 @@
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E82" t="n">
-        <v>175</v>
+        <v>427</v>
       </c>
       <c r="F82" t="n">
-        <v>129.28</v>
+        <v>159.01</v>
       </c>
       <c r="G82" t="n">
-        <v>75.42</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>304.28</v>
+        <v>586.01</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="83">
@@ -3151,22 +3163,22 @@
         <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E83" t="n">
-        <v>177</v>
+        <v>320</v>
       </c>
       <c r="F83" t="n">
-        <v>130.63</v>
+        <v>266.53</v>
       </c>
       <c r="G83" t="n">
-        <v>76.2</v>
+        <v>155.47</v>
       </c>
       <c r="H83" t="n">
-        <v>307.63</v>
+        <v>586.53</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>46.53</v>
       </c>
     </row>
     <row r="84">
@@ -3184,22 +3196,22 @@
         <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E84" t="n">
-        <v>144</v>
+        <v>423</v>
       </c>
       <c r="F84" t="n">
-        <v>156.16</v>
+        <v>158.53</v>
       </c>
       <c r="G84" t="n">
-        <v>91.09</v>
+        <v>92.48</v>
       </c>
       <c r="H84" t="n">
-        <v>300.16</v>
+        <v>581.53</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="85">
@@ -3217,22 +3229,22 @@
         <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E85" t="n">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="F85" t="n">
-        <v>138.63</v>
+        <v>209.01</v>
       </c>
       <c r="G85" t="n">
-        <v>80.87</v>
+        <v>121.92</v>
       </c>
       <c r="H85" t="n">
-        <v>306.63</v>
+        <v>585.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>45.01</v>
       </c>
     </row>
   </sheetData>
